--- a/untranslated/downloads/data-excel/9.5.1.xlsx
+++ b/untranslated/downloads/data-excel/9.5.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -1255,7 +1255,7 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1291,6 +1291,9 @@
     </xf>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="109" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="110">
@@ -1705,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.85546875" customWidth="1"/>
@@ -1714,7 +1717,7 @@
     <col min="4" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="43.5" customHeight="1">
+    <row r="1" spans="1:13" ht="43.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -1729,7 +1732,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -1744,7 +1747,7 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1">
+    <row r="3" spans="1:13" ht="15.75" thickBot="1">
       <c r="A3" s="4"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1757,8 +1760,9 @@
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
+      <c r="M3" s="4"/>
     </row>
-    <row r="4" spans="1:12" ht="15.75" thickBot="1">
+    <row r="4" spans="1:13" ht="15.75" thickBot="1">
       <c r="A4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1795,8 +1799,11 @@
       <c r="L4" s="9">
         <v>2023</v>
       </c>
+      <c r="M4" s="16">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" ht="40.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:13" ht="40.5" customHeight="1" thickBot="1">
       <c r="A5" s="7" t="s">
         <v>6</v>
       </c>
@@ -1833,8 +1840,11 @@
       <c r="L5" s="13">
         <v>0.11972285283622097</v>
       </c>
+      <c r="M5" s="13">
+        <v>0.08</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" ht="36.75" customHeight="1">
+    <row r="6" spans="1:13" ht="36.75" customHeight="1">
       <c r="A6" s="14" t="s">
         <v>12</v>
       </c>
@@ -1852,7 +1862,7 @@
       <c r="I6" s="10"/>
       <c r="J6" s="10"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:13">
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -1861,17 +1871,17 @@
       <c r="I7" s="11"/>
       <c r="J7" s="11"/>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:13">
       <c r="H8" s="11"/>
       <c r="I8" s="11"/>
       <c r="J8" s="11"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:13">
       <c r="D10" s="12"/>
       <c r="E10" s="12"/>
       <c r="F10" s="12"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:13">
       <c r="G13" s="12"/>
       <c r="H13" s="11"/>
       <c r="I13" s="11"/>
